--- a/research/traditional_assets/database/data/denmark/denmark_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.11</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0793</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="G2">
-        <v>0.05050564096568656</v>
+        <v>0.1067830264996446</v>
       </c>
       <c r="H2">
-        <v>0.05050564096568656</v>
+        <v>0.1067830264996446</v>
       </c>
       <c r="I2">
-        <v>0.08361099744743866</v>
+        <v>0.05782854901576251</v>
       </c>
       <c r="J2">
-        <v>0.06499519001959142</v>
+        <v>0.04540194455291589</v>
       </c>
       <c r="K2">
-        <v>324.7</v>
+        <v>166.5</v>
       </c>
       <c r="L2">
-        <v>0.06326844761403713</v>
+        <v>0.04081582624469884</v>
       </c>
       <c r="M2">
-        <v>273</v>
+        <v>100.4</v>
       </c>
       <c r="N2">
-        <v>0.05568928236302069</v>
+        <v>0.02167951458616743</v>
       </c>
       <c r="O2">
-        <v>0.8407761010163228</v>
+        <v>0.603003003003003</v>
       </c>
       <c r="P2">
-        <v>273</v>
+        <v>100.4</v>
       </c>
       <c r="Q2">
-        <v>0.05568928236302069</v>
+        <v>0.02167951458616743</v>
       </c>
       <c r="R2">
-        <v>0.8407761010163228</v>
+        <v>0.603003003003003</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>387.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="V2">
-        <v>0.07908694055730081</v>
+        <v>0.01448899829414178</v>
       </c>
       <c r="W2">
-        <v>0.3271536523929471</v>
+        <v>0.1586772133803488</v>
       </c>
       <c r="X2">
-        <v>0.04473029039676673</v>
+        <v>0.07710369696334629</v>
       </c>
       <c r="Y2">
-        <v>0.2824233619961803</v>
+        <v>0.08157351641700253</v>
       </c>
       <c r="Z2">
-        <v>5.994043447792572</v>
+        <v>4.735662874390528</v>
       </c>
       <c r="AA2">
-        <v>0.3895839928749651</v>
+        <v>0.215008303244381</v>
       </c>
       <c r="AB2">
-        <v>0.04369172504312197</v>
+        <v>0.07430763168185987</v>
       </c>
       <c r="AC2">
-        <v>0.3458922678318432</v>
+        <v>0.1407006715625211</v>
       </c>
       <c r="AD2">
-        <v>199.8</v>
+        <v>346.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>199.8</v>
+        <v>346.1</v>
       </c>
       <c r="AG2">
-        <v>-187.9</v>
+        <v>279</v>
       </c>
       <c r="AH2">
-        <v>0.03916111328890631</v>
+        <v>0.06953708912641646</v>
       </c>
       <c r="AI2">
-        <v>0.159955167720759</v>
+        <v>0.3420636489424788</v>
       </c>
       <c r="AJ2">
-        <v>-0.03985745497740915</v>
+        <v>0.05682165332681615</v>
       </c>
       <c r="AK2">
-        <v>-0.2181332714186208</v>
+        <v>0.2953318513813909</v>
       </c>
       <c r="AL2">
-        <v>13.7</v>
+        <v>9.49</v>
       </c>
       <c r="AM2">
-        <v>13.7</v>
+        <v>9.49</v>
       </c>
       <c r="AN2">
-        <v>0.4592047805102276</v>
+        <v>1.443888193575303</v>
       </c>
       <c r="AO2">
-        <v>31.32116788321168</v>
+        <v>24.85774499473129</v>
       </c>
       <c r="AP2">
-        <v>-0.4318547460353941</v>
+        <v>1.1639549436796</v>
       </c>
       <c r="AQ2">
-        <v>31.32116788321168</v>
+        <v>24.85774499473129</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0793</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="G3">
-        <v>0.05050564096568656</v>
+        <v>0.1067830264996446</v>
       </c>
       <c r="H3">
-        <v>0.05050564096568656</v>
+        <v>0.1067830264996446</v>
       </c>
       <c r="I3">
-        <v>0.08361099744743866</v>
+        <v>0.05782854901576251</v>
       </c>
       <c r="J3">
-        <v>0.06499519001959142</v>
+        <v>0.04540194455291589</v>
       </c>
       <c r="K3">
-        <v>324.7</v>
+        <v>166.5</v>
       </c>
       <c r="L3">
-        <v>0.06326844761403713</v>
+        <v>0.04081582624469884</v>
       </c>
       <c r="M3">
-        <v>273</v>
+        <v>100.4</v>
       </c>
       <c r="N3">
-        <v>0.05568928236302069</v>
+        <v>0.02167951458616743</v>
       </c>
       <c r="O3">
-        <v>0.8407761010163228</v>
+        <v>0.603003003003003</v>
       </c>
       <c r="P3">
-        <v>273</v>
+        <v>100.4</v>
       </c>
       <c r="Q3">
-        <v>0.05568928236302069</v>
+        <v>0.02167951458616743</v>
       </c>
       <c r="R3">
-        <v>0.8407761010163228</v>
+        <v>0.603003003003003</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>387.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="V3">
-        <v>0.07908694055730081</v>
+        <v>0.01448899829414178</v>
       </c>
       <c r="W3">
-        <v>0.3271536523929471</v>
+        <v>0.1586772133803488</v>
       </c>
       <c r="X3">
-        <v>0.04473029039676673</v>
+        <v>0.07710369696334629</v>
       </c>
       <c r="Y3">
-        <v>0.2824233619961803</v>
+        <v>0.08157351641700253</v>
       </c>
       <c r="Z3">
-        <v>5.994043447792572</v>
+        <v>4.735662874390528</v>
       </c>
       <c r="AA3">
-        <v>0.3895839928749651</v>
+        <v>0.215008303244381</v>
       </c>
       <c r="AB3">
-        <v>0.04369172504312197</v>
+        <v>0.07430763168185987</v>
       </c>
       <c r="AC3">
-        <v>0.3458922678318432</v>
+        <v>0.1407006715625211</v>
       </c>
       <c r="AD3">
-        <v>199.8</v>
+        <v>346.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>199.8</v>
+        <v>346.1</v>
       </c>
       <c r="AG3">
-        <v>-187.9</v>
+        <v>279</v>
       </c>
       <c r="AH3">
-        <v>0.03916111328890631</v>
+        <v>0.06953708912641646</v>
       </c>
       <c r="AI3">
-        <v>0.159955167720759</v>
+        <v>0.3420636489424788</v>
       </c>
       <c r="AJ3">
-        <v>-0.03985745497740915</v>
+        <v>0.05682165332681615</v>
       </c>
       <c r="AK3">
-        <v>-0.2181332714186208</v>
+        <v>0.2953318513813909</v>
       </c>
       <c r="AL3">
-        <v>13.7</v>
+        <v>9.49</v>
       </c>
       <c r="AM3">
-        <v>13.7</v>
+        <v>9.49</v>
       </c>
       <c r="AN3">
-        <v>0.4592047805102276</v>
+        <v>1.443888193575303</v>
       </c>
       <c r="AO3">
-        <v>31.32116788321168</v>
+        <v>24.85774499473129</v>
       </c>
       <c r="AP3">
-        <v>-0.4318547460353941</v>
+        <v>1.1639549436796</v>
       </c>
       <c r="AQ3">
-        <v>31.32116788321168</v>
+        <v>24.85774499473129</v>
       </c>
     </row>
   </sheetData>
